--- a/consolidado_limpio.xlsx
+++ b/consolidado_limpio.xlsx
@@ -1524,12 +1524,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1538,47 +1538,47 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>78000</v>
+        <v>90600</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>127500</v>
+        <v>98500</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1590,12 +1590,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>86700</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1616,35 +1616,35 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>98800</v>
+        <v>125200</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1656,61 +1656,61 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>40200</v>
+        <v>34000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sin vendedor</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>18200</v>
+        <v>133400</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1722,24 +1722,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>159900</v>
+        <v>164400</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1755,45 +1755,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1805,28 +1805,28 @@
         <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>174100</v>
+        <v>107500</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1835,43 +1835,43 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>87300</v>
+        <v>152700</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Sin vendedor</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>25600</v>
+        <v>65900</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1880,19 +1880,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>26700</v>
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Sin especificar</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>26700</v>
+        <v>157700</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1946,64 +1946,64 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Sin especificar</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>134400</v>
+        <v>144100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>46400</v>
+        <v>78100</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2019,12 +2019,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2033,31 +2033,31 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>90600</v>
+        <v>72700</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2066,14 +2066,14 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>98500</v>
+        <v>78000</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2085,28 +2085,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>127500</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2118,12 +2118,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2132,64 +2132,64 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>125200</v>
+        <v>86700</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>34000</v>
+        <v>98800</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sin vendedor</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2201,7 +2201,7 @@
         <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>133400</v>
+        <v>40200</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2210,118 +2210,118 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>164400</v>
+        <v>18200</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>159900</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>107500</v>
+        <v>36200</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2330,14 +2330,14 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>152700</v>
+        <v>174100</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sin vendedor</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2349,12 +2349,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,31 +2363,31 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>65900</v>
+        <v>87300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Sin especificar</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2399,23 +2399,23 @@
         <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2429,80 +2429,80 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>157700</v>
+        <v>26700</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>144100</v>
+        <v>26700</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>78100</v>
+        <v>134400</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2528,19 +2528,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>72700</v>
+        <v>46400</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Sin especificar</t>
         </is>
       </c>
     </row>
